--- a/results/reliability_eval/Llama-3-8B_P176_sample_15_tokens_0.1_temp_direct_query_scores_08-24-4.xlsx
+++ b/results/reliability_eval/Llama-3-8B_P176_sample_15_tokens_0.1_temp_direct_query_scores_08-24-4.xlsx
@@ -477,31 +477,31 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.4759493789900244</v>
+        <v>0.6392191251561297</v>
       </c>
       <c r="B2" t="n">
-        <v>0.8698886270519708</v>
+        <v>0.8851848020307997</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4759493789900244</v>
+        <v>0.6392191251561297</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8698886270519708</v>
+        <v>0.8851848020307997</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5167263701238259</v>
+        <v>0.3610785728615898</v>
       </c>
       <c r="F2" t="n">
-        <v>0.877397648889823</v>
+        <v>0.7893115059846258</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9992995421167931</v>
+        <v>0.9998414434470841</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9998622324820071</v>
+        <v>0.9999347896239572</v>
       </c>
       <c r="I2" t="n">
-        <v>0.879</v>
+        <v>0.8090000000000001</v>
       </c>
     </row>
   </sheetData>
